--- a/AI_docs/Inquiry_Types.xlsx
+++ b/AI_docs/Inquiry_Types.xlsx
@@ -2963,14 +2963,14 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Расширение запасного классификатора на оставшиеся типы</t>
+          <t>Расширение запасного классификатора на оставшиеся типы, устранение ложных срабатываний, подбор порогов</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>

--- a/AI_docs/Inquiry_Types.xlsx
+++ b/AI_docs/Inquiry_Types.xlsx
@@ -2932,14 +2932,14 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Выбор модели эмбеддингов для MVP: сравнить кандидатов (e5-small, BGE-M3 и др.) по качеству на размеченном наборе, подобрать пороги k-NN</t>
+          <t>Выбор модели эмбеддингов для MVP: тест 4–5 кандидатов (e5-small, e5-large, BGE-M3, модели, дообученные на русском) на размеченном наборе, пороги поиска и k-NN под каждую модель</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>

--- a/AI_docs/Inquiry_Types.xlsx
+++ b/AI_docs/Inquiry_Types.xlsx
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>

--- a/AI_docs/Inquiry_Types.xlsx
+++ b/AI_docs/Inquiry_Types.xlsx
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Разметить эталонный набор и проанализировать все 16 типов и 6 тем: слова, пересечения, «спор против заявки», тип-статус против типа-темы</t>
+          <t>Разметить эталонный набор и проанализировать все 16 типов и 6 тем: слова, пересечения, «спор против заявки», тип-статус против типа-темы; отметить число задач в каждой реплике и посчитать долю реплик с двумя и более (триггер 4 перехода на LangGraph, ADR-200)</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
